--- a/naver-place-crawler/results_health/부평_PT.xlsx
+++ b/naver-place-crawler/results_health/부평_PT.xlsx
@@ -422,17 +422,17 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="37" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>필라테스 린 산곡점</t>
+          <t>아이언휘트니스 헬스&amp;PT 삼산점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>pilateslean_sangok@naver.com</t>
+          <t>ironfitnesssamsan@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1311-1654</t>
+          <t>0507-1483-2126</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천 부평구 원적로 412 5층</t>
+          <t>인천광역시 부평구 부평북로 448 로얄프라자 2층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/pilateslean_sangok/224258799074</t>
+          <t>https://blog.naver.com/ironfitnesssamsan</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -612,22 +612,22 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>710</v>
       </c>
       <c r="Q2" t="n">
-        <v>2</v>
+        <v>291</v>
       </c>
       <c r="R2" t="n">
-        <v>2</v>
+        <v>1001</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2024471908</t>
+          <t>1098353648</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2024471908</t>
+          <t>https://m.place.naver.com/place/1098353648</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -675,7 +675,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천 부평구 부평대로 55 국천빌딩 12층 바디소나타</t>
+          <t>인천광역시 부평구 부평대로 55 국천빌딩 12층 바디소나타</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -700,14 +700,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4p44e</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -722,10 +718,10 @@
         <v>939</v>
       </c>
       <c r="Q3" t="n">
-        <v>2336</v>
+        <v>2337</v>
       </c>
       <c r="R3" t="n">
-        <v>3275</v>
+        <v>3276</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -756,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>부평PT 여성 교정 전문 웰니스8</t>
+          <t>바디채널 부평점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>thestorygym_gn@naver.com</t>
+          <t>bodych19@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1378-9205</t>
+          <t>0507-1375-3433</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천 부평구 부평대로 68 8층</t>
+          <t>인천광역시 부평구 경원대로 1422 대덕아크로존 3층 바디채널 부평점</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/thestorygym_gn</t>
+          <t>https://blog.naver.com/bodych19</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -798,14 +794,10 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w04dt6z</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -817,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>74</v>
+        <v>855</v>
       </c>
       <c r="Q4" t="n">
-        <v>909</v>
+        <v>2433</v>
       </c>
       <c r="R4" t="n">
-        <v>983</v>
+        <v>3288</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -832,12 +824,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1174367491</t>
+          <t>1913225220</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1174367491</t>
+          <t>https://m.place.naver.com/place/1913225220</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -854,29 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>바디채널 부평점</t>
+          <t>부평PT 여성 교정 전문 웰니스8</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>bodych19@naver.com</t>
+          <t>thestorygym_gn@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1375-3433</t>
+          <t>0507-1378-9205</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천 부평구 경원대로 1422 대덕아크로존 3층 바디채널 부평점</t>
+          <t>인천광역시 부평구 부평대로 68 8층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bodych19</t>
+          <t>https://blog.naver.com/thestorygym_gn</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -896,14 +888,10 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4q8r0</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -915,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>855</v>
+        <v>74</v>
       </c>
       <c r="Q5" t="n">
-        <v>2432</v>
+        <v>910</v>
       </c>
       <c r="R5" t="n">
-        <v>3287</v>
+        <v>984</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -930,12 +918,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1913225220</t>
+          <t>1174367491</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1913225220</t>
+          <t>https://m.place.naver.com/place/1174367491</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -969,7 +957,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천 부평구 수변로 8 파워프라자 5층 501호, 502호</t>
+          <t>인천광역시 부평구 수변로 8 파워프라자 5층 501호, 502호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -994,14 +982,10 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w47zgs</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1067,7 +1051,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천 부평구 시장로 82 2층</t>
+          <t>인천광역시 부평구 시장로 82 2층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1092,14 +1076,10 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4fs1c</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1165,7 +1145,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천 부평구 원적로 295 더 루츠 스퀘어 5층</t>
+          <t>인천광역시 부평구 원적로 295 더 루츠 스퀘어 5층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1190,14 +1170,10 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w40cxc</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>O</t>
@@ -1212,10 +1188,10 @@
         <v>986</v>
       </c>
       <c r="Q8" t="n">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="R8" t="n">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1263,7 +1239,7 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천 부평구 체육관로 34 7층</t>
+          <t>인천광역시 부평구 체육관로 34 7층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1288,14 +1264,10 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wcbsfx</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1307,13 +1279,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="Q9" t="n">
         <v>458</v>
       </c>
       <c r="R9" t="n">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1361,7 +1333,7 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천 부평구 경원대로 1358 2층</t>
+          <t>인천광역시 부평구 경원대로 1358 2층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1386,14 +1358,10 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wzebqsn</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1459,7 +1427,7 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>인천 부평구 굴포로 42 지하층 B01호, B02호</t>
+          <t>인천광역시 부평구 굴포로 42 지하층 B01호, B02호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1484,14 +1452,10 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4e2iv</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>

--- a/naver-place-crawler/results_health/부평_PT.xlsx
+++ b/naver-place-crawler/results_health/부평_PT.xlsx
@@ -422,7 +422,7 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>아이언휘트니스 헬스&amp;PT 삼산점</t>
+          <t>필라테스 린 산곡점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ironfitnesssamsan@naver.com</t>
+          <t>pilateslean_sangok@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1483-2126</t>
+          <t>0507-1311-1654</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천광역시 부평구 부평북로 448 로얄프라자 2층</t>
+          <t>인천 부평구 원적로 412 5층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ironfitnesssamsan</t>
+          <t>https://blog.naver.com/pilateslean_sangok/224258799074</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -612,22 +612,22 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>710</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>291</v>
+        <v>2</v>
       </c>
       <c r="R2" t="n">
-        <v>1001</v>
+        <v>2</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1098353648</t>
+          <t>2024471908</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1098353648</t>
+          <t>https://m.place.naver.com/place/2024471908</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -1094,10 +1094,10 @@
         <v>44</v>
       </c>
       <c r="Q7" t="n">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="R7" t="n">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>

--- a/naver-place-crawler/results_health/부평_PT.xlsx
+++ b/naver-place-crawler/results_health/부평_PT.xlsx
@@ -426,13 +426,13 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="37" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -586,7 +586,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/pilateslean_sangok/224258799074</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,12 +596,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>bs77773@naver.com</t>
+          <t>eoghehfdl@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -675,12 +675,12 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천광역시 부평구 부평대로 55 국천빌딩 12층 바디소나타</t>
+          <t>인천 부평구 부평대로 55 국천빌딩 12층 바디소나타</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bs77773</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -690,20 +690,24 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4p44e</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -740,7 +744,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -757,7 +761,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>bodych19@naver.com</t>
+          <t>bcno19@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -769,12 +773,12 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천광역시 부평구 경원대로 1422 대덕아크로존 3층 바디채널 부평점</t>
+          <t>인천 부평구 경원대로 1422 대덕아크로존 3층 바디채널 부평점</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bodych19</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -784,20 +788,24 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4q8r0</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -834,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -851,7 +859,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>thestorygym_gn@naver.com</t>
+          <t>burugi221212@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -863,12 +871,12 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천광역시 부평구 부평대로 68 8층</t>
+          <t>인천 부평구 부평대로 68 8층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/thestorygym_gn</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -878,20 +886,24 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w04dt6z</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -928,7 +940,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -945,7 +957,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>histrionics92934@naver.com</t>
+          <t>tim90999@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -957,12 +969,12 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천광역시 부평구 수변로 8 파워프라자 5층 501호, 502호</t>
+          <t>인천 부평구 수변로 8 파워프라자 5층 501호, 502호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/turningpointgym_bupyeong</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -972,7 +984,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -982,10 +994,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w47zgs</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1022,7 +1038,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1051,12 +1067,12 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천광역시 부평구 시장로 82 2층</t>
+          <t>인천 부평구 시장로 82 2층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/restpt</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1066,20 +1082,24 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4fs1c</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1094,10 +1114,10 @@
         <v>44</v>
       </c>
       <c r="Q7" t="n">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="R7" t="n">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1116,7 +1136,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1165,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천광역시 부평구 원적로 295 더 루츠 스퀘어 5층</t>
+          <t>인천 부평구 원적로 295 더 루츠 스퀘어 5층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1170,10 +1190,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w40cxc</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>O</t>
@@ -1210,7 +1234,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1239,12 +1263,12 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천광역시 부평구 체육관로 34 7층</t>
+          <t>인천 부평구 체육관로 34 7층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/msgym_01/223768835115</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1254,20 +1278,24 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wcbsfx</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1304,41 +1332,41 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>무무바디짐 부평점</t>
+          <t>3세트짐 체형교정센터 부평본점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>qudan79@naver.com</t>
+          <t>lineup_pt@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1440-0638</t>
+          <t>0507-1323-8788</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천광역시 부평구 경원대로 1358 2층</t>
+          <t>인천 부평구 경원대로 1404 1003호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/qudan79</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1348,20 +1376,24 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4eq6k9</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1369,17 +1401,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>23</v>
+        <v>369</v>
       </c>
       <c r="Q10" t="n">
-        <v>5</v>
+        <v>456</v>
       </c>
       <c r="R10" t="n">
-        <v>28</v>
+        <v>825</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,17 +1420,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2061355439</t>
+          <t>1774897291</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2061355439</t>
+          <t>https://m.place.naver.com/place/1774897291</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1410,29 +1442,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>그루비짐24 헬스PT 갈산점</t>
+          <t>무무바디짐 부평점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>groovygs2@naver.com</t>
+          <t>qudan79@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1379-2744</t>
+          <t>0507-1440-0638</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>인천광역시 부평구 굴포로 42 지하층 B01호, B02호</t>
+          <t>인천 부평구 경원대로 1358 2층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/groovygym24_gs/</t>
+          <t>https://blog.naver.com/qudan79</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1447,15 +1479,19 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wzebqsn</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1463,17 +1499,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>815</v>
+        <v>23</v>
       </c>
       <c r="Q11" t="n">
-        <v>839</v>
+        <v>5</v>
       </c>
       <c r="R11" t="n">
-        <v>1654</v>
+        <v>28</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,17 +1518,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1574242499</t>
+          <t>2061355439</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1574242499</t>
+          <t>https://m.place.naver.com/place/2061355439</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/부평_PT.xlsx
+++ b/naver-place-crawler/results_health/부평_PT.xlsx
@@ -417,17 +417,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>바디소나타 부평점 24시 헬스 PT</t>
+          <t>필라테스 린 산곡점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>eoghehfdl@naver.com</t>
+          <t>pilateslean_sangok@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1330-3214</t>
+          <t>0507-1311-1654</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천광역시 부평구 부평대로 55 국천빌딩 12층 바디소나타</t>
+          <t>인천 부평구 원적로 412 5층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/pilateslean_sangok/224258799074</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,12 +596,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4p44e</t>
+          <t>https://talk.naver.com/ct/wgildz7</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -621,17 +621,17 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>938</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>2340</v>
+        <v>3</v>
       </c>
       <c r="R2" t="n">
-        <v>3278</v>
+        <v>3</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,17 +640,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1699883683</t>
+          <t>2024471908</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1699883683</t>
+          <t>https://m.place.naver.com/place/2024471908</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -662,29 +662,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>터닝포인트짐 헬스 PT 부평점</t>
+          <t>바디소나타 부평점 24시 헬스 PT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>tim90999@naver.com</t>
+          <t>bs77773@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1334-5777</t>
+          <t>0507-1330-3214</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천광역시 부평구 수변로 8 파워프라자 5층 501호, 502호</t>
+          <t>인천광역시 부평구 부평대로 55 국천빌딩 12층 바디소나타</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/bs77773</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -694,24 +694,20 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w47zgs</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -723,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>232</v>
+        <v>938</v>
       </c>
       <c r="Q3" t="n">
-        <v>4998</v>
+        <v>2340</v>
       </c>
       <c r="R3" t="n">
-        <v>5230</v>
+        <v>3278</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,17 +734,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1179482808</t>
+          <t>1699883683</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1179482808</t>
+          <t>https://m.place.naver.com/place/1699883683</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -760,29 +756,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>바디채널 부평점</t>
+          <t>터닝포인트짐 헬스 PT 부평점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>bcno19@naver.com</t>
+          <t>tim90999@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1375-3433</t>
+          <t>0507-1334-5777</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천광역시 부평구 경원대로 1422 대덕아크로존 3층 바디채널 부평점</t>
+          <t>인천광역시 부평구 수변로 8 파워프라자 5층 501호, 502호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/turningpointgym_bupyeong</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -792,7 +788,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -802,14 +798,10 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4q8r0</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -821,13 +813,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>857</v>
+        <v>232</v>
       </c>
       <c r="Q4" t="n">
-        <v>2436</v>
+        <v>4998</v>
       </c>
       <c r="R4" t="n">
-        <v>3293</v>
+        <v>5230</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,17 +828,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1913225220</t>
+          <t>1179482808</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1913225220</t>
+          <t>https://m.place.naver.com/place/1179482808</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -858,29 +850,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>부평PT 여성 교정 전문 웰니스8</t>
+          <t>바디채널 부평점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>burugi221212@naver.com</t>
+          <t>bodych19@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1378-9205</t>
+          <t>0507-1375-3433</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천광역시 부평구 부평대로 68 8층</t>
+          <t>인천광역시 부평구 경원대로 1422 대덕아크로존 3층 바디채널 부평점</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/bodych19</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -890,24 +882,20 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w04dt6z</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -919,13 +907,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>74</v>
+        <v>860</v>
       </c>
       <c r="Q5" t="n">
-        <v>913</v>
+        <v>2436</v>
       </c>
       <c r="R5" t="n">
-        <v>987</v>
+        <v>3296</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,17 +922,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1174367491</t>
+          <t>1913225220</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1174367491</t>
+          <t>https://m.place.naver.com/place/1913225220</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -956,29 +944,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>레스트 앤 피트니스 PT</t>
+          <t>부평PT 여성 교정 전문 웰니스8</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>restpt@naver.com</t>
+          <t>thestorygym_gn@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1356-7156</t>
+          <t>0507-1378-9205</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천광역시 부평구 시장로 82 2층</t>
+          <t>인천광역시 부평구 부평대로 68 8층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/thestorygym_gn</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -988,24 +976,20 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4fs1c</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1017,13 +1001,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="Q6" t="n">
-        <v>588</v>
+        <v>913</v>
       </c>
       <c r="R6" t="n">
-        <v>632</v>
+        <v>987</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,47 +1016,51 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1802861183</t>
+          <t>1174367491</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1802861183</t>
+          <t>https://m.place.naver.com/place/1174367491</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>온정필라테스&amp;PT 산곡점</t>
+          <t>레스트 앤 피트니스 PT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ktg191800@naver.com</t>
+          <t>restpt@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0507-1356-7156</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천광역시 부평구 마장로 320 2층 207호, 산곡역 2번출구에서 도보 2분 한화프라자 2층</t>
+          <t>인천 부평구 시장로 82 2층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/restpt</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1082,12 +1070,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1097,7 +1085,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4lmji</t>
+          <t>https://talk.naver.com/ct/w4fs1c</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1107,17 +1095,17 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>328</v>
+        <v>44</v>
       </c>
       <c r="Q7" t="n">
-        <v>610</v>
+        <v>588</v>
       </c>
       <c r="R7" t="n">
-        <v>938</v>
+        <v>632</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1126,17 +1114,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1452652224</t>
+          <t>1802861183</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1452652224</t>
+          <t>https://m.place.naver.com/place/1802861183</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1153,12 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천광역시 부평구 부평대로 19-1 도시프라자빌딩 7층 701호</t>
+          <t>인천 부평구 부평대로 19-1 도시프라자빌딩 7층 701호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/fpeoplew1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1180,12 +1168,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1209,13 +1197,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="Q8" t="n">
         <v>924</v>
       </c>
       <c r="R8" t="n">
-        <v>2104</v>
+        <v>2105</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1234,7 +1222,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1288,14 +1276,10 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w40cxc</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>O</t>
@@ -1332,41 +1316,41 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>엠에스짐 헬스장 헬스 PT 삼산점</t>
+          <t>3세트짐 체형교정센터 부평본점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>msgym_01@naver.com</t>
+          <t>lineup_pt@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>032-330-3334</t>
+          <t>0507-1323-8788</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천광역시 부평구 체육관로 34 7층</t>
+          <t>인천 부평구 경원대로 1404 1003호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/lineup_pt</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1376,12 +1360,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1391,7 +1375,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wcbsfx</t>
+          <t>https://talk.naver.com/ct/w4eq6k9</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1405,13 +1389,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>900</v>
+        <v>369</v>
       </c>
       <c r="Q10" t="n">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="R10" t="n">
-        <v>1360</v>
+        <v>825</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,17 +1404,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1350569862</t>
+          <t>1774897291</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1350569862</t>
+          <t>https://m.place.naver.com/place/1774897291</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1459,12 +1443,12 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>인천광역시 부평구 경원대로 1358 2층</t>
+          <t>인천 부평구 경원대로 1358 2층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/qudan79</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1474,12 +1458,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1528,7 +1512,105 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>그루비짐24 헬스PT 갈산점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>groovygs2@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1379-2744</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>인천 부평구 굴포로 42 지하층 B01호, B02호</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/groovygym24_gs/</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4e2iv</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>817</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>840</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1657</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1574242499</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1574242499</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/부평_PT.xlsx
+++ b/naver-place-crawler/results_health/부평_PT.xlsx
@@ -417,16 +417,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="37" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>필라테스 린 산곡점</t>
+          <t>그린짐</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>pilateslean_sangok@naver.com</t>
+          <t>green_gym@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1311-1654</t>
+          <t>0507-1482-4423</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천 부평구 원적로 412 5층</t>
+          <t>인천 부평구 부평북로 339 2층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/pilateslean_sangok/224258799074</t>
+          <t>https://blog.naver.com/green_gym</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -611,27 +611,27 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wgildz7</t>
+          <t>https://talk.naver.com/ct/w4fs9p</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Q2" t="n">
-        <v>3</v>
+        <v>822</v>
       </c>
       <c r="R2" t="n">
-        <v>3</v>
+        <v>1143</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,12 +640,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2024471908</t>
+          <t>1527477204</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2024471908</t>
+          <t>https://m.place.naver.com/place/1527477204</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -679,7 +679,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천광역시 부평구 부평대로 55 국천빌딩 12층 바디소나타</t>
+          <t>인천 부평구 부평대로 55 국천빌딩 12층 바디소나타</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -704,10 +704,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4p44e</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -773,7 +777,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천광역시 부평구 수변로 8 파워프라자 5층 501호, 502호</t>
+          <t>인천 부평구 수변로 8 파워프라자 5층 501호, 502호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -798,10 +802,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w47zgs</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -867,7 +875,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천광역시 부평구 경원대로 1422 대덕아크로존 3층 바디채널 부평점</t>
+          <t>인천 부평구 경원대로 1422 대덕아크로존 3층 바디채널 부평점</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -892,10 +900,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4q8r0</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -961,7 +973,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천광역시 부평구 부평대로 68 8층</t>
+          <t>인천 부평구 부평대로 68 8층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -986,10 +998,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w04dt6z</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1004,10 +1020,10 @@
         <v>74</v>
       </c>
       <c r="Q6" t="n">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="R6" t="n">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1200,10 +1216,10 @@
         <v>1181</v>
       </c>
       <c r="Q8" t="n">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="R8" t="n">
-        <v>2105</v>
+        <v>2106</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1251,7 +1267,7 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천광역시 부평구 원적로 295 더 루츠 스퀘어 5층</t>
+          <t>인천 부평구 원적로 295 더 루츠 스퀘어 5층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1276,10 +1292,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w40cxc</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>O</t>
@@ -1511,104 +1531,6 @@
         </is>
       </c>
       <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>헬스장</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>그루비짐24 헬스PT 갈산점</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>groovygs2@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1379-2744</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>인천 부평구 굴포로 42 지하층 B01호, B02호</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/groovygym24_gs/</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4e2iv</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>817</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>840</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1657</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1574242499</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1574242499</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
